--- a/medford_gibkaya_endoskopiya.xlsx
+++ b/medford_gibkaya_endoskopiya.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Гибкая эндоскопия для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Aohua, Pentax, Fujifilm — всего 20 позиций.</t>
+          <t>Гибкая эндоскопия для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Aohua, Pentax, Fujifilm.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_gibkaya_endoskopiya.xlsx
+++ b/medford_gibkaya_endoskopiya.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать гибкая эндоскопия для клиники?</t>
+          <t>Чем гибкий эндоскоп отличается от жёсткого?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм, Угол поля зрения, °). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>У гибкого эндоскопа рабочая часть изгибается и проходит извилистые каналы — пищевод, кишечник, бронхи, мочевыводящие пути. Жёсткий эндоскоп имеет прямую несгибаемую трубку и стержне-линзовую оптику, его применяют там, где путь к органу короткий и прямой. Гибкий вариант менее травматичен для протяжённых полостей.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какие бывают виды гибких эндоскопов?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>По принципу передачи изображения — фиброскопы и видеоэндоскопы. Фиброскоп передаёт картинку по оптоволокну в окуляр, проще и дешевле, годится для диагностики. Видеоэндоскоп оснащён чип-камерой, выводит изображение высокого разрешения на монитор, позволяет запись и обработку. По назначению — гастроскопы, колоноскопы, бронхоскопы, риноларингоскопы.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что важнее при выборе — диаметр или длина?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены SonoScape, Aohua, Pentax, Fujifilm. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Оба параметра решают разные задачи. Диаметр вводимой трубки влияет на проходимость и переносимость: для гортани нужен тонкий эндоскоп 5,7–5,8 мм. Рабочая длина определяет досягаемость: колоноскопу нужно 1650–1700 мм, гастроскопу — около 1050 мм. Подбирайте по области исследования, а не по одному числу.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что такое ультразвуковой видеоэндоскоп?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Это гибкий эндоскоп с встроенным ультразвуковым датчиком на дистальном конце — конвексным (EG-UC5T) или радиальным (EG-UR5). Он сочетает эндоскопический осмотр слизистой с УЗИ стенки органа и прилежащих структур, что применяют в эндосонографии ЖКТ. Инструментальный канал позволяет проводить прицельные манипуляции.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Можно ли использовать эндоскоп с чужим процессором?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Только при подтверждённой совместимости. Эндоскоп, видеопроцессор и источник света составляют одну платформу с общим коннектором и протоколом. Например, видеопроцессор Aohua AQ-200 рассчитан на эндоскопы Aohua FHD-GT/CL. Смешивание брендов без официальной совместимости приводит к потере функций или отказу распознавания.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Чем отличается гибкий эндоскоп от жесткого?</t>
+          <t>Как обрабатывают гибкий эндоскоп?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Гибкий эндоскоп нельзя целиком автоклавировать: высокая температура повреждает оптику и электронику. Между пациентами его очищают и подвергают химической дезинфекции по инструкции производителя. Правильная обработка каналов критична — недостаточная дезинфекция названа в источниках основным путём инфекционных осложнений.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какие бывают виды эндоскопии?</t>
+          <t>Опасна ли гибкая эндоскопия?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Метод считается малоинвазивным и информативным, но, как у любой процедуры, есть риски: инфекционные осложнения при плохой обработке, перфорация стенки, кровотечение, реакции на седацию. Противопоказания зависят от органа и решаются врачом, который взвешивает пользу и риск в конкретном случае.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Гибкая эндоскопия для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов SonoScape, Aohua, Pentax, Fujifilm.</t>
+          <t>Гибкая эндоскопия — метод осмотра внутренних органов гибким эндоскопом, рабочая часть которого изгибается и проходит извилистые участки: пищевод, желудок, толстую кишку, бронхи, мочевыводящие пути. В категории представлены видеоэндоскопические системы SonoScape HD-500 и HD-330, Pentax IMAGINA EPK-i5500c, видеопроцессор Aohua AQ-200, гастроскопы, колоноскопы и риноларингоскопы с разрешением 1920×1080 (Full HD). Диаметр вводимой трубки моделей — от 5,6 мм у гастроскопа SonoScape EG-330L до 12,8 мм у колоноскопа Aohua HD-CL1IL, рабочая длина — от 600 до 1700 мм. Источники света — ксеноновые лампы 300 Вт и светодиодные модули.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Фиброскоп и видеоэндоскоп</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое гибкая эндоскопия</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4498,247 +4498,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Фиброскоп и видеоэндоскоп</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Фиброскоп</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр вводимой трубки, мм</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Глубина резкости, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Угол поля зрения, °</t>
+          <t>Видеоэндоскоп</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape HD-500 видеоэндоскопическая система</t>
+          <t>Передача изображения</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>По оптоволокну в окуляр</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Чип-камера на монитор</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Видеоколоноскоп Aohua HD-CL1IL</t>
+          <t>Разрешение</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>Ограничено волоконным жгутом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>12,8</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2-100</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>140</t>
+          <t>До 1920×1080 (Full HD)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Источник света Aohua AQL-200</t>
+          <t>Запись и обработка</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>Затруднена</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Запись, программная обработка картинки</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Видеогастроскоп Pentax EG29-V10c</t>
+          <t>Типичное применение</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>Базовая диагностика</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>3-100</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>140°</t>
+          <t>Диагностика и лечебные манипуляции</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопическая кушетка 19-LV200</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
+          <t>Пример из каталога</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Фиброволоконные модели</t>
+        </is>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Видеоэндоскопическая система на базе SonoScape HD-330 (FullHD)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>SonoScape</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>SonoScape EG-500, Pentax EG29-V10c</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4750,7 +4629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5076,12 +4955,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите область исследования</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается гибкая эндоскопия: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Гастроскопия, колоноскопия, бронхоскопия и ЛОР требуют разных эндоскопов. Для верхних отделов ЖКТ берут гастроскоп с трубкой около 9,3–9,6 мм, для толстой кишки — колоноскоп с рабочей длиной 1650–1700 мм, для гортани — тонкий риноларингоскоп 5,7–5,8 мм.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5121,12 +5000,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Сверьте диаметр и рабочую длину</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Диаметр вводимой трубки определяет проходимость и переносимость процедуры, рабочая длина — досягаемость органа. В каталоге трубки от 5,6 мм (SonoScape EG-330L) до 12,8 мм (Aohua HD-CL1IL), длина от 600 до 1700 мм. Тонкий эндоскоп менее травматичен.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5166,12 +5045,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Выберите фиброскоп или видеоэндоскоп</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм, Угол поля зрения, °. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Фиброскоп передаёт картинку по оптоволокну в окуляр и подходит для простой диагностики. Видеоэндоскоп с чип-камерой выводит Full HD на монитор, позволяет записывать процедуру и применять программную обработку изображения, поэтому его берут и для лечебных манипуляций.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5211,12 +5090,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Проверьте совместимость с процессором и светом</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: SonoScape, Aohua, Pentax, Fujifilm.</t>
+          <t>Эндоскоп работает в связке с видеопроцессором и источником света одной платформы. Видеопроцессор Aohua AQ-200 совместим с эндоскопами Aohua FHD-GT/CL, система Pentax IMAGINA EPK-i5500c — со своей линейкой. Убедитесь, что коннектор и протокол совпадают.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5256,12 +5135,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Оцените источник света</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Яркость и цветопередача зависят от источника: ксеноновая лампа 300 Вт (SonoScape HD-500) даёт мощный поток с цветовой температурой около 5900 К, светодиодный модуль (Pentax) служит дольше и меньше греется. Автоматическая и ручная регулировка яркости упрощает работу.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5301,12 +5180,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Учтите обработку и парк расходников</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Гибкий эндоскоп нельзя автоклавировать целиком — он проходит химическую дезинфекцию между пациентами. Заложите совместимые моющие средства, тест-полоски и запасные клапаны воздуха и воды, чтобы не простаивать между процедурами.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5356,7 +5235,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Гибкая эндоскопия подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены SonoScape, Aohua, Pentax, Fujifilm. При выборе обращают внимание на диаметр вводимой трубки, рабочая длина, глубина резкости, угол поля зрения, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>При подборе гибкого эндоскопа отталкивайтесь от области исследования: для гастроскопии критичны диаметр вводимой трубки и глубина резкости, для колоноскопии — рабочая длина 1650–1700 мм и угол поля зрения. Видеоэндоскоп с чип-камерой и Full HD, как SonoScape EG-500 или Pentax EG29-V10c, даёт документируемую картинку и программную обработку, тогда как фиброскоп проще и дешевле для базовой диагностики. Всегда проверяйте совместимость эндоскопа с видеопроцессором и источником света.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5640,13 +5519,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое гибкая эндоскопия</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Гибкая эндоскопия — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов SonoScape, Aohua, Pentax, Fujifilm. Подберём вариант под задачи вашего отделения.</t>
+          <t>Гибкая эндоскопия использует эндоскоп с подвижным дистальным концом, на котором расположены камера, световод и рабочий канал для инструментов. По принципу передачи изображения различают фиброскопы (оптоволокно, окуляр) и видеоэндоскопы (чип-камера, изображение на мониторе, запись и программная обработка). Метод применяют в гастроэнтерологии, пульмонологии, урологии, гинекологии и ЛОР для диагностики и лечебных манипуляций. В каталоге — системы и эндоскопы SonoScape, Pentax, Aohua и Fujifilm с разрешением Full HD, диаметром вводимой трубки 5,6–12,8 мм и рабочей длиной 600–1700 мм.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5683,13 +5562,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое гибкая эндоскопия</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм, Угол поля зрения, °), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Гибкая эндоскопия — исследование внутренних органов эндоскопом с подвижной рабочей частью. Тонкая трубка с камерой, световодом и рабочим каналом плавно изгибается и проходит извилистые участки тела с минимальным травмированием тканей. Через рабочий канал вводят инструменты для биопсии, удаления полипов и остановки кровотечения, поэтому метод сочетает диагностику и лечение.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5726,13 +5605,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Из чего состоит гибкий эндоскоп</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные элементы — коннектор с разъёмами для света, воды, аспиратора и видеопроцессора; рукоятка с клапанами подачи воздуха и воды, переключателем изгиба дистального конца и входом для инструментов; рабочая дистальная часть, меняющая положение в разных плоскостях. На кончике расположены объектив камеры, выход световода и отверстие рабочего канала.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5769,13 +5648,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Где применяют гибкие эндоскопы</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Гастроэнтерология использует гастроскопию, дуоденоскопию и колоноскопию; пульмонология — бронхоскопию; урология и гинекология — цистоскопию, уретерореноскопию, гистероскопию; ЛОР — назофарингоскопию и ларингоскопию. Под каждую область подбирают эндоскоп с нужным диаметром трубки, рабочей длиной и углом поля зрения из линеек SonoScape, Pentax, Aohua и Fujifilm.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5792,6 +5671,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как подобрать оборудование для гибкой эндоскопии</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Отталкивайтесь от области исследования и совместимости: эндоскоп, видеопроцессор и источник света должны работать на одной платформе. Сверяйте диаметр вводимой трубки, рабочую длину, глубину резкости и угол поля зрения с задачами кабинета. Видеоэндоскоп с Full HD и чип-камерой предпочтителен для документирования и лечебных манипуляций, фиброскоп — для базовой диагностики.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>gibkaya_endoskopiya</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
